--- a/public/templates/template_users.xlsx
+++ b/public/templates/template_users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\web\starter-pack\laravel\portal-kampus\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBAF0F26-5092-437A-AA93-1AC4CF93E5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25D41F5-FB00-46B1-A6E9-4FF71FC31F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{97952424-84AD-471A-97CD-52406DF5C35E}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="15375" windowHeight="7875" xr2:uid="{97952424-84AD-471A-97CD-52406DF5C35E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,25 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>nim</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>username</t>
   </si>
@@ -404,10 +391,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5124B3-DF16-4545-84C1-2EA2B1502C98}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,9 +410,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
